--- a/data/raw/individual/ID 010/continuous/mHLEA_excel/TUM_S010_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 010/continuous/mHLEA_excel/TUM_S010_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 010/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 010/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA10EC1-D5E6-AD49-B4AF-1FCAE9CE949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366C8B34-DA7D-434E-9BE2-CD5887443A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,10 +68,10 @@
     <t>W</t>
   </si>
   <si>
-    <t>8: restaurant</t>
+    <t>restaurant</t>
   </si>
   <si>
-    <t>8: Sport outdoor</t>
+    <t>Sport outdoor</t>
   </si>
 </sst>
 </file>
@@ -623,7 +623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>45495.624999999964</v>
@@ -635,7 +635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>45495.666666666628</v>
@@ -647,7 +647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>45495.708333333292</v>
@@ -655,11 +655,14 @@
       <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>45495.749999999956</v>
@@ -671,7 +674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>45495.791666666621</v>
@@ -683,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>45495.833333333285</v>
@@ -695,7 +698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>45495.874999999949</v>
@@ -707,7 +710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>45495.916666666613</v>
@@ -719,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>45495.958333333278</v>
@@ -731,7 +734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>45495.999999999942</v>
@@ -743,7 +746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>45496.041666666606</v>
@@ -755,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>45496.08333333327</v>
@@ -767,7 +770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>45496.124999999935</v>
@@ -779,7 +782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>45496.166666666599</v>
@@ -791,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>45496.208333333263</v>
@@ -803,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>45496.249999999927</v>
@@ -1391,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>45498.291666666475</v>
@@ -1403,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>45498.333333333139</v>
@@ -1415,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>45498.374999999804</v>
@@ -1427,7 +1430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>45498.416666666468</v>
@@ -1439,7 +1442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>45498.458333333132</v>
@@ -1451,7 +1454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>45498.499999999796</v>
@@ -1463,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>45498.541666666461</v>
@@ -1475,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>45498.583333333125</v>
@@ -1487,7 +1490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>45498.624999999789</v>
@@ -1499,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>45498.666666666453</v>
@@ -1511,7 +1514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>45498.708333333117</v>
@@ -1523,7 +1526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>45498.749999999782</v>
@@ -1531,11 +1534,14 @@
       <c r="B92" t="s">
         <v>5</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>45498.791666666446</v>
@@ -1543,11 +1549,14 @@
       <c r="B93" t="s">
         <v>5</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>45498.83333333311</v>
@@ -1559,7 +1568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>45498.874999999774</v>
@@ -1571,7 +1580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>45498.916666666439</v>
